--- a/excel/upload4supplier/[FUS]上传订单成功.xlsx
+++ b/excel/upload4supplier/[FUS]上传订单成功.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:R6"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -434,16 +434,37 @@
         <v>发货数量</v>
       </c>
       <c r="H1" s="2" t="str">
-        <v>入库数量</v>
+        <v>出库数量</v>
       </c>
       <c r="I1" s="2" t="str">
+        <v>订单日期</v>
+      </c>
+      <c r="J1" s="2" t="str">
+        <v>订货人</v>
+      </c>
+      <c r="K1" s="2" t="str">
+        <v>接单人</v>
+      </c>
+      <c r="L1" s="2" t="str">
+        <v>接单日期</v>
+      </c>
+      <c r="M1" s="2" t="str">
         <v>拣货人</v>
       </c>
-      <c r="J1" s="2" t="str">
-        <v>结算数量</v>
-      </c>
-      <c r="K1" s="2" t="str">
-        <v>订单日期</v>
+      <c r="N1" s="2" t="str">
+        <v>拣货日期</v>
+      </c>
+      <c r="O1" s="2" t="str">
+        <v>发货人</v>
+      </c>
+      <c r="P1" s="2" t="str">
+        <v>发货日期</v>
+      </c>
+      <c r="Q1" s="2" t="str">
+        <v>出库人</v>
+      </c>
+      <c r="R1" s="2" t="str">
+        <v>出库日期</v>
       </c>
     </row>
     <row r="2">
@@ -472,13 +493,34 @@
         <v>3</v>
       </c>
       <c r="I2" s="2" t="str">
-        <v>测试拣货人</v>
-      </c>
-      <c r="J2" s="2">
-        <v>9</v>
+        <v>2026-09-01</v>
+      </c>
+      <c r="J2" s="2" t="str">
+        <v>张三</v>
       </c>
       <c r="K2" s="2" t="str">
-        <v>2026-09-01</v>
+        <v>阿大</v>
+      </c>
+      <c r="L2" s="2" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="M2" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N2" s="2" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="O2" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P2" s="2" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R2" s="2" t="str">
+        <v>2026-08-31</v>
       </c>
     </row>
     <row r="3">
@@ -507,13 +549,34 @@
         <v/>
       </c>
       <c r="I3" s="2" t="str">
-        <v>测试拣货人</v>
-      </c>
-      <c r="J3" s="2">
-        <v>5</v>
+        <v>2026-09-01</v>
+      </c>
+      <c r="J3" s="2" t="str">
+        <v>张三</v>
       </c>
       <c r="K3" s="2" t="str">
-        <v>2026-09-01</v>
+        <v>阿大</v>
+      </c>
+      <c r="L3" s="2" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="M3" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N3" s="2" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="O3" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P3" s="2" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="Q3" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R3" s="2" t="str">
+        <v>2026-08-31</v>
       </c>
     </row>
     <row r="4">
@@ -542,13 +605,34 @@
         <v>2</v>
       </c>
       <c r="I4" s="2" t="str">
-        <v>测试拣货人</v>
+        <v>2026-09-01</v>
       </c>
       <c r="J4" s="2" t="str">
-        <v/>
+        <v>李四</v>
       </c>
       <c r="K4" s="2" t="str">
-        <v>2026-09-01</v>
+        <v>阿大</v>
+      </c>
+      <c r="L4" s="2" t="str">
+        <v>2026-08-28</v>
+      </c>
+      <c r="M4" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N4" s="2" t="str">
+        <v>2026-08-29</v>
+      </c>
+      <c r="O4" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P4" s="2" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R4" s="2" t="str">
+        <v>2026-08-31</v>
       </c>
     </row>
     <row r="5">
@@ -577,12 +661,33 @@
         <v/>
       </c>
       <c r="I5" s="2" t="str">
-        <v>测试拣货人</v>
+        <v>2026-09-02</v>
       </c>
       <c r="J5" s="2" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="K5" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="L5" s="2" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="M5" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N5" s="2" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="O5" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P5" s="2" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="Q5" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R5" s="2" t="str">
         <v>2026-09-02</v>
       </c>
     </row>
@@ -612,18 +717,39 @@
         <v/>
       </c>
       <c r="I6" s="2" t="str">
-        <v>测试拣货人</v>
+        <v>2026-09-02</v>
       </c>
       <c r="J6" s="2" t="str">
-        <v/>
+        <v>张三</v>
       </c>
       <c r="K6" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="L6" s="2" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="M6" s="2" t="str">
+        <v>阿二</v>
+      </c>
+      <c r="N6" s="2" t="str">
+        <v>2026-09-01</v>
+      </c>
+      <c r="O6" s="2" t="str">
+        <v>测试操作人</v>
+      </c>
+      <c r="P6" s="2" t="str">
+        <v>2026-09-02</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <v>阿大</v>
+      </c>
+      <c r="R6" s="2" t="str">
         <v>2026-09-02</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R6"/>
   </ignoredErrors>
 </worksheet>
 </file>